--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD61C0-1CA3-4ACD-A1FA-2A83E6DB9A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A27480-3520-45B2-9667-666BE5864D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách trường Hàn" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="388">
   <si>
     <t>DANH SÁCH TRƯỜNG HÀN QUỐC - KỲ THÁNG 3/2027</t>
   </si>
@@ -1826,6 +1826,9 @@
   </si>
   <si>
     <t>DANG THUY DUONG.pdf</t>
+  </si>
+  <si>
+    <t>DO QUOC CUONG.pdf</t>
   </si>
 </sst>
 </file>
@@ -2137,6 +2140,61 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>58783</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>336372</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42A4906A-29C6-6038-E33B-F3AB60027970}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7831183" y="1"/>
+          <a:ext cx="7592789" cy="5151120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2966,6 +3024,7 @@
     <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -36117,7 +36176,7 @@
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="40" t="s">
         <v>194</v>
       </c>
     </row>
@@ -36347,6 +36406,7 @@
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
     <hyperlink ref="B8" r:id="rId2" xr:uid="{ED442877-600F-4277-A187-78503CD85686}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{E4032478-3FD4-4BB5-8FF3-125CAEE952EC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36542,7 +36602,7 @@
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="40" t="s">
         <v>206</v>
       </c>
     </row>
@@ -36771,6 +36831,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{2BA41946-9368-4D7B-84DA-634E055E0F3B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36968,7 +37029,9 @@
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="18"/>
+      <c r="B28" s="40" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
@@ -37196,6 +37259,7 @@
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
     <hyperlink ref="B8" r:id="rId2" xr:uid="{2FAF74E8-571B-41A9-BD9A-1AF128D0F4FE}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{244134E0-40D6-488E-BEE9-F65F1001D30D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A27480-3520-45B2-9667-666BE5864D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F239B4-40C1-4CF5-A11F-49E392329727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách trường Hàn" sheetId="1" r:id="rId1"/>
@@ -2106,6 +2106,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2118,9 +2121,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2491,13 +2491,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
@@ -2772,13 +2772,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
     </row>
     <row r="20" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
@@ -3039,20 +3039,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -3103,14 +3103,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -3121,14 +3121,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -3155,14 +3155,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="345" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -3173,14 +3173,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -3207,14 +3207,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -3233,14 +3233,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -3465,20 +3465,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -3516,7 +3516,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="35" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3529,14 +3529,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -3547,14 +3547,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -3581,14 +3581,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -3599,14 +3599,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -3633,14 +3633,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -3659,14 +3659,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -3875,6 +3875,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{37F6E222-FD54-4F41-A332-5202D5A1EC9E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3891,20 +3892,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -3942,7 +3943,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="35" t="s">
         <v>258</v>
       </c>
     </row>
@@ -3955,14 +3956,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -3973,14 +3974,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -4007,14 +4008,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -4025,14 +4026,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -4059,14 +4060,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -4085,14 +4086,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -4301,6 +4302,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{503C9A51-8587-4D75-965C-6221AEB61EB0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4317,20 +4319,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -4381,14 +4383,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -4399,14 +4401,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -4433,14 +4435,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -4451,14 +4453,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -4485,14 +4487,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -4511,14 +4513,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -4743,20 +4745,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -4807,14 +4809,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -4825,14 +4827,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -4859,14 +4861,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -4877,14 +4879,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -4911,14 +4913,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -4937,14 +4939,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -5169,20 +5171,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -5233,14 +5235,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="400.2" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -5251,14 +5253,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -5285,14 +5287,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="300" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -5303,14 +5305,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -5337,14 +5339,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -5361,14 +5363,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -5593,20 +5595,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -5657,14 +5659,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -5675,14 +5677,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -5709,14 +5711,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -5727,14 +5729,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -5761,14 +5763,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -5787,14 +5789,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -34289,20 +34291,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -34353,14 +34355,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="207" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -34371,14 +34373,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -34405,14 +34407,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -34423,14 +34425,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -34457,14 +34459,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -34483,14 +34485,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -34715,20 +34717,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -34779,14 +34781,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="248.4" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -34797,14 +34799,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -34831,14 +34833,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="400.2" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -34849,14 +34851,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="138" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -34883,20 +34885,20 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="35" t="s">
         <v>386</v>
       </c>
     </row>
@@ -34909,14 +34911,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -35142,20 +35144,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -35206,14 +35208,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="345" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -35224,14 +35226,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -35258,14 +35260,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -35276,14 +35278,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -35310,20 +35312,20 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="35" t="s">
         <v>384</v>
       </c>
     </row>
@@ -35336,14 +35338,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -35569,20 +35571,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -35620,7 +35622,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="35" t="s">
         <v>171</v>
       </c>
     </row>
@@ -35633,14 +35635,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="207" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -35651,14 +35653,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -35685,14 +35687,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="303.60000000000002" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -35703,14 +35705,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -35737,14 +35739,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -35763,14 +35765,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -35979,6 +35981,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{CFA510EA-C4A1-4686-A9E0-33B55BA1E450}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35995,20 +35998,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -36046,7 +36049,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="35" t="s">
         <v>185</v>
       </c>
     </row>
@@ -36059,14 +36062,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -36077,14 +36080,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="138" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -36111,14 +36114,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -36129,14 +36132,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -36163,20 +36166,20 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="35" t="s">
         <v>194</v>
       </c>
     </row>
@@ -36189,14 +36192,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -36423,20 +36426,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -36487,14 +36490,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -36505,14 +36508,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -36539,14 +36542,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -36557,14 +36560,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -36589,20 +36592,20 @@
       <c r="B25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="35" t="s">
         <v>206</v>
       </c>
     </row>
@@ -36615,14 +36618,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -36848,20 +36851,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -36899,7 +36902,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="35" t="s">
         <v>211</v>
       </c>
     </row>
@@ -36912,14 +36915,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="207" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -36930,14 +36933,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -36964,14 +36967,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -36982,14 +36985,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -37016,20 +37019,20 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="35" t="s">
         <v>387</v>
       </c>
     </row>
@@ -37042,14 +37045,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -37276,20 +37279,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -37327,7 +37330,7 @@
       <c r="A8" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="35" t="s">
         <v>223</v>
       </c>
     </row>
@@ -37335,7 +37338,7 @@
       <c r="A9" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="35" t="s">
         <v>225</v>
       </c>
     </row>
@@ -37348,14 +37351,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="36"/>
+      <c r="B12" s="37"/>
     </row>
     <row r="13" spans="1:2" ht="193.2" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
@@ -37366,14 +37369,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="36"/>
+      <c r="B15" s="37"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
@@ -37400,14 +37403,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="36"/>
+      <c r="B20" s="37"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
@@ -37418,14 +37421,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="37"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
@@ -37452,20 +37455,20 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="36"/>
+      <c r="B28" s="37"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="35" t="s">
         <v>385</v>
       </c>
     </row>
@@ -37478,14 +37481,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="36"/>
+      <c r="B32" s="37"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">

--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB7D3FE-260B-4164-9581-2AB9890D19A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B819918C-01FD-4232-97FA-D2B1D12DB8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách trường Hàn" sheetId="1" r:id="rId1"/>
@@ -2273,22 +2273,22 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2312,23 +2312,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>58783</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>670560</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>336372</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5384598E-6236-AF03-6BAC-7CD83A3DEB58}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2337,22 +2337,25 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7831183" y="1"/>
-          <a:ext cx="7592789" cy="5151120"/>
+          <a:off x="7734300" y="0"/>
+          <a:ext cx="8770620" cy="5847080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2656,13 +2659,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
@@ -2937,13 +2940,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="20" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
@@ -3204,20 +3207,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -3268,14 +3271,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -3286,14 +3289,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -3320,14 +3323,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="345" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -3338,14 +3341,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -3372,14 +3375,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -3398,14 +3401,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -3630,20 +3633,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -3694,14 +3697,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -3712,14 +3715,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -3746,14 +3749,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -3764,14 +3767,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -3798,14 +3801,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -3824,14 +3827,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -4057,20 +4060,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -4121,14 +4124,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -4139,14 +4142,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -4173,14 +4176,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -4191,14 +4194,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -4225,14 +4228,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -4251,14 +4254,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -4484,20 +4487,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>348</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -4548,14 +4551,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -4566,14 +4569,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -4600,14 +4603,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -4618,14 +4621,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -4652,14 +4655,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -4678,14 +4681,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -4910,20 +4913,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -4974,14 +4977,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -4992,14 +4995,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -5026,14 +5029,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -5044,14 +5047,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -5078,14 +5081,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -5104,14 +5107,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -5336,20 +5339,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -5400,14 +5403,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="400.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -5418,14 +5421,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -5452,14 +5455,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="300" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -5470,14 +5473,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -5504,14 +5507,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -5528,14 +5531,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -5760,20 +5763,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -5824,14 +5827,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -5842,14 +5845,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -5876,14 +5879,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -5894,14 +5897,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -5928,14 +5931,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -5954,14 +5957,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -6186,20 +6189,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="50"/>
+      <c r="B1" s="46"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="50"/>
+      <c r="B3" s="46"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
@@ -6237,7 +6240,7 @@
       <c r="A8" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="44" t="s">
         <v>392</v>
       </c>
     </row>
@@ -6250,14 +6253,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="50"/>
+      <c r="B11" s="46"/>
     </row>
     <row r="12" spans="1:2" ht="317.39999999999998" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
@@ -6268,14 +6271,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="50"/>
+      <c r="B14" s="46"/>
     </row>
     <row r="15" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
@@ -6302,14 +6305,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="50"/>
+      <c r="B19" s="46"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
@@ -6320,14 +6323,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="50"/>
+      <c r="B22" s="46"/>
     </row>
     <row r="23" spans="1:3" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
@@ -6354,14 +6357,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="50"/>
+      <c r="B27" s="46"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36" t="s">
@@ -6380,14 +6383,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="50"/>
+      <c r="B31" s="46"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
@@ -34882,20 +34885,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -34946,14 +34949,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -34964,14 +34967,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -34998,14 +35001,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -35016,14 +35019,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -35050,14 +35053,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -35076,14 +35079,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -35308,20 +35311,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -35372,14 +35375,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="248.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -35390,14 +35393,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -35424,14 +35427,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="400.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -35442,14 +35445,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -35476,14 +35479,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -35502,14 +35505,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -35735,20 +35738,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -35799,14 +35802,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -35817,14 +35820,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -35851,14 +35854,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -35869,14 +35872,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -35903,14 +35906,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -35929,14 +35932,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -36162,20 +36165,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -36226,14 +36229,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -36244,14 +36247,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -36278,14 +36281,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -36296,14 +36299,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -36330,14 +36333,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -36356,14 +36359,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -36589,20 +36592,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -36653,14 +36656,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="358.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -36671,14 +36674,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -36705,14 +36708,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="358.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -36723,14 +36726,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -36757,14 +36760,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -36783,14 +36786,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -37017,20 +37020,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -37081,14 +37084,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -37099,14 +37102,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -37133,14 +37136,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -37151,14 +37154,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -37183,14 +37186,14 @@
       <c r="B25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -37209,14 +37212,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -37442,20 +37445,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -37506,14 +37509,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
@@ -37524,14 +37527,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
@@ -37558,14 +37561,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="45"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -37576,14 +37579,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="45"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
@@ -37610,14 +37613,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="45"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
@@ -37636,14 +37639,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
@@ -37870,20 +37873,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="47"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="45"/>
+      <c r="B3" s="47"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -37942,14 +37945,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
-      <c r="B11" s="45"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="47"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="45"/>
+      <c r="B12" s="47"/>
     </row>
     <row r="13" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
@@ -37960,14 +37963,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="45"/>
+      <c r="B15" s="47"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
@@ -37994,14 +37997,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="B20" s="45"/>
+      <c r="B20" s="47"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
@@ -38012,14 +38015,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="45"/>
-      <c r="B22" s="45"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B23" s="45"/>
+      <c r="B23" s="47"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
@@ -38046,14 +38049,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="47"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B28" s="45"/>
+      <c r="B28" s="47"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
@@ -38072,14 +38075,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="45"/>
+      <c r="B32" s="47"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">

--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\Desktop\Thư mục mới\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAD2EC4-273D-45CC-8C1B-9903DD8A61DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9836C0-8DD2-479F-9958-98DCD1F96662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="420">
   <si>
     <t>Daewon 대원대학교  |  Chi phí thấp - Hỗ trợ E7 liên kết Samsung &amp; Hyundai - Có thể học Online</t>
   </si>
@@ -1635,9 +1635,6 @@
     <t>200</t>
   </si>
   <si>
-    <t>Cập nhật sau (đang xác nhận với trường)</t>
-  </si>
-  <si>
     <t>Đại học Nữ sinh Dongduk Catalog.pdf</t>
   </si>
   <si>
@@ -1766,18 +1763,6 @@
     <t>Catholic Kwandong University | 가톨릭관동대학교 - Trường ĐH tư thục 70 năm truyền thống tại Gangneung, Gangwon-do</t>
   </si>
   <si>
-    <t>D2-2 (Đại học 4 năm) - Nhập học tháng 3</t>
-  </si>
-  <si>
-    <t>Không giới hạn (정원 외)</t>
-  </si>
-  <si>
-    <t>Không có MOU cụ thể - Đây là chương trình tuyển sinh 순수외국인 (thuần nước ngoài), không cần MOU</t>
-  </si>
-  <si>
-    <t>TalkFile_가톨릭관동대학교_학부_모집_국문_pdf.pdf</t>
-  </si>
-  <si>
     <t>24, Beomil-ro 579 beon-gil, Gangneung-si, Gangwon-do 25601, Hàn Quốc (cách Seoul ~3 giờ, gần biển Gangneung)</t>
   </si>
   <si>
@@ -1803,35 +1788,6 @@
 4: Track Tiếng Anh: TOEFL iBT 71 / IELTS 5.5 / CEFR B2 / TEPS 601 trở lên
 5: Không phân biệt vùng miền tại Việt Nam
 6: Có sức khỏe tốt (cần nộp giấy khám bao gồm viêm gan, lao phổi)</t>
-  </si>
-  <si>
-    <t>Các ngành tuyển sinh (Track Hàn Quốc - D2-2 Đại học 4 năm):
-■ Tự chọn ngành (자율전공학부) - Chọn ngành sau năm 1
-■ Kinh doanh - Quản trị (경영학전공)
-■ Hành chính học (행정학전공)
-■ Cảnh sát - An ninh hàng hải (경찰행정학전공 / 해양경찰학전공)
-■ Công tác xã hội (사회복지학전공)
-■ Quảng cáo &amp; PR (광고홍보학전공)
-■ Quản trị khách sạn &amp; du lịch (호텔관광경영학전공)
-■ Ẩm thực &amp; kinh doanh nhà hàng (조리외식경영학전공)
-■ Quản trị y tế (의료경영학전공)
-■ Logistics hàng không (항공교통물류전공)
-■ Truyền thông đa phương tiện (미디어콘텐츠전공)
-■ Khoa học Y sinh (의생명과학전공)
-■ Kỹ thuật xây dựng / Kiến trúc 5 năm (건축공학전공 / 건축학전공)
-■ AI &amp; Phần mềm (AI·소프트웨어융합학부)
-■ Điều khiển máy bay (항공운항전공)
-■ Kỹ thuật bảo trì hàng không (항공정비학전공)
-■ Cảng thông minh (스마트항만공학전공)
-■ Thể thao - Giải trí - Huấn luyện (스포츠레저/재활의학/지도학전공)
-■ Âm nhạc thực dụng (실용음악전공)
-■ CG Design (CG디자인전공)</t>
-  </si>
-  <si>
-    <t>- Vào thẳng chương trình đại học D2-2 (không qua D2-6)
-- Thời gian học: 4 năm (riêng Kiến trúc 5 năm)
-- Điều kiện tốt nghiệp: Đạt TOPIK 4 trở lên (hoặc tương đương)
-- Từ năm 2, một số ngành yêu cầu TOPIK 3 (ngành khoa học xã hội) hoặc TOPIK 2 (ngành thể dục/nghệ thuật)</t>
   </si>
   <si>
     <t>Hồ sơ nộp lần đầu (bản gốc + bản scan):
@@ -1884,9 +1840,6 @@
 - Gangneung có nhiều cơ hội việc làm thêm (du lịch, dịch vụ, khu resort biển)</t>
   </si>
   <si>
-    <t>https://ipsi.cku.ac.kr | Email: irc@cku.ac.kr</t>
-  </si>
-  <si>
     <t>Nội dung hồ sơ</t>
   </si>
   <si>
@@ -2107,6 +2060,37 @@
   </si>
   <si>
     <t>TalkFile_가톨릭관동대학교_학부_모집_국문_.pdf</t>
+  </si>
+  <si>
+    <t>Các ngành tuyển sinh (Track Hàn Quốc - D2-2 Đại học 4 năm):
+■ Tự chọn ngành (자율전공학부) - Chọn ngành sau năm 1
+■ Kinh doanh - Quản trị (경영학전공)
+■ Hành chính học (행정학전공)
+■ Công tác xã hội (사회복지학전공)
+■ Quảng cáo &amp; PR (광고홍보학전공)
+■ Quản trị khách sạn &amp; du lịch (호텔관광경영학전공)
+■ Ẩm thực &amp; kinh doanh nhà hàng (조리외식경영학전공)
+■ Quản trị y tế (의료경영학전공)
+■ Logistics hàng không (항공교통물류전공)
+■ Truyền thông đa phương tiện (미디어콘텐츠전공)
+■ Khoa học Y sinh (의생명과학전공)
+■ Kỹ thuật xây dựng / Kiến trúc 5 năm (건축공학전공 / 건축학전공)
+■ AI &amp; Phần mềm (AI·소프트웨어융합학부)
+■ Điều khiển máy bay (항공운항전공)
+■ Kỹ thuật bảo trì hàng không (항공정비학전공)
+■ Cảng thông minh (스마트항만공학전공)
+■ Thể thao - Giải trí - Huấn luyện (스포츠레저/재활의학/지도학전공)
+■ Âm nhạc thực dụng (실용음악전공)
+■ CG Design (CG디자인전공)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3fEWfRndKeg</t>
+  </si>
+  <si>
+    <t>D2-6 (6 tháng): Học tiếng Hàn &amp; văn hóa → chuyển D2-2 (Đại học 4 năm)
+- Điều kiện chuyển: Hoàn thành khóa tiếng, đủ điều kiện từ trường
+- Học bổng chuyên ngành kỳ đầu tiên: Giảm 50%
+- Học bổng các kỳ tiếp theo: 30%–60% tùy trình độ TOPIK</t>
   </si>
 </sst>
 </file>
@@ -2421,14 +2405,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2803,10 +2787,10 @@
       <c r="A1" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
@@ -3098,11 +3082,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
     </row>
     <row r="20" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45" t="s">
@@ -3371,17 +3355,17 @@
       <c r="A1" s="49" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -3432,14 +3416,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -3450,14 +3434,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -3484,14 +3468,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="345" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -3502,14 +3486,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -3536,14 +3520,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -3562,14 +3546,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -3797,17 +3781,17 @@
       <c r="A1" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -3858,14 +3842,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -3876,14 +3860,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -3910,14 +3894,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -3928,14 +3912,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -3962,14 +3946,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -3988,14 +3972,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -4224,17 +4208,17 @@
       <c r="A1" s="49" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -4285,14 +4269,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -4303,14 +4287,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -4337,14 +4321,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -4355,14 +4339,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -4389,14 +4373,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -4415,14 +4399,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -4651,17 +4635,17 @@
       <c r="A1" s="49" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -4712,14 +4696,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -4730,14 +4714,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -4764,14 +4748,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -4782,14 +4766,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -4816,14 +4800,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -4842,14 +4826,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -5077,17 +5061,17 @@
       <c r="A1" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -5138,14 +5122,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -5156,14 +5140,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -5190,14 +5174,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -5208,14 +5192,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -5242,14 +5226,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -5268,14 +5252,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -5503,17 +5487,17 @@
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -5564,14 +5548,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -5582,14 +5566,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -5616,14 +5600,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="300" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -5634,14 +5618,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -5668,14 +5652,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -5692,14 +5676,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -5928,17 +5912,17 @@
       <c r="A1" s="49" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -5989,14 +5973,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -6007,14 +5991,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -6041,14 +6025,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -6059,14 +6043,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -6093,14 +6077,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -6119,14 +6103,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -6354,17 +6338,17 @@
       <c r="A1" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
@@ -6395,7 +6379,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>325</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6403,7 +6387,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6411,43 +6395,43 @@
         <v>11</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="220.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -6455,7 +6439,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -6463,43 +6447,43 @@
         <v>21</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
@@ -6507,7 +6491,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -6515,25 +6499,25 @@
         <v>31</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6541,18 +6525,18 @@
         <v>35</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
@@ -6778,26 +6762,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="B1" s="47"/>
+        <v>337</v>
+      </c>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6805,15 +6789,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>340</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>341</v>
+      <c r="B6" s="18">
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6821,7 +6805,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>342</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6829,7 +6813,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6837,43 +6821,43 @@
         <v>11</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -6881,7 +6865,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>347</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -6889,43 +6873,43 @@
         <v>21</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>348</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -6933,7 +6917,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -6941,44 +6925,42 @@
         <v>31</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>343</v>
-      </c>
+      <c r="B28" s="18"/>
     </row>
     <row r="29" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
-        <v>353</v>
+      <c r="B29" s="44" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
@@ -7209,13 +7191,13 @@
         <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -7245,13 +7227,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -7281,13 +7263,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -7317,13 +7299,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -7353,13 +7335,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -7389,10 +7371,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="4"/>
@@ -7423,13 +7405,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -7459,13 +7441,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -7495,13 +7477,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -7531,10 +7513,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="4"/>
@@ -7565,10 +7547,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="4"/>
@@ -7599,10 +7581,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="4"/>
@@ -7633,10 +7615,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="4"/>
@@ -7667,13 +7649,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -7703,13 +7685,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -7739,10 +7721,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="4"/>
@@ -7773,10 +7755,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="4"/>
@@ -7807,10 +7789,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="4"/>
@@ -7841,10 +7823,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="4"/>
@@ -7875,10 +7857,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="4"/>
@@ -7909,10 +7891,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="4"/>
@@ -7943,10 +7925,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="4"/>
@@ -7977,10 +7959,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="4"/>
@@ -8011,10 +7993,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="4"/>
@@ -8045,13 +8027,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -8081,7 +8063,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="10"/>
@@ -8113,10 +8095,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="4"/>
@@ -8147,10 +8129,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="4"/>
@@ -8181,10 +8163,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="4"/>
@@ -8215,7 +8197,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="10"/>
@@ -8247,7 +8229,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="10"/>
@@ -8279,7 +8261,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="10"/>
@@ -8311,7 +8293,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="10"/>
@@ -8343,13 +8325,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -8379,11 +8361,11 @@
         <v>33</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="7" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -8413,11 +8395,11 @@
         <v>34</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="7" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -8447,13 +8429,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -8483,13 +8465,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -8519,13 +8501,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -35477,17 +35459,17 @@
       <c r="A1" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -35538,14 +35520,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -35556,14 +35538,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -35590,14 +35572,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -35608,14 +35590,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -35642,14 +35624,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -35668,14 +35650,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -35903,17 +35885,17 @@
       <c r="A1" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -35964,14 +35946,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="248.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -35982,14 +35964,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -36016,14 +35998,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -36034,14 +36016,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -36068,14 +36050,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -36094,14 +36076,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -36330,17 +36312,17 @@
       <c r="A1" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -36391,14 +36373,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -36409,14 +36391,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -36443,14 +36425,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -36461,14 +36443,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -36495,14 +36477,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -36521,14 +36503,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -36757,17 +36739,17 @@
       <c r="A1" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -36818,14 +36800,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -36836,14 +36818,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -36870,14 +36852,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -36888,14 +36870,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -36922,14 +36904,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -36948,14 +36930,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -37184,17 +37166,17 @@
       <c r="A1" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -37245,14 +37227,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -37263,14 +37245,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -37297,14 +37279,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -37315,14 +37297,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -37349,14 +37331,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -37375,14 +37357,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -37612,17 +37594,17 @@
       <c r="A1" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -37673,14 +37655,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -37691,14 +37673,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -37725,14 +37707,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -37743,14 +37725,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -37775,14 +37757,14 @@
       <c r="B25" s="18"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -37801,14 +37783,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -38037,17 +38019,17 @@
       <c r="A1" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -38098,14 +38080,14 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="47"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
@@ -38116,14 +38098,14 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="47"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
@@ -38150,14 +38132,14 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="47"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
@@ -38168,14 +38150,14 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="47"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:3" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
@@ -38202,14 +38184,14 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
     </row>
     <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="47"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
@@ -38228,14 +38210,14 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="47"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
@@ -38465,17 +38447,17 @@
       <c r="A1" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="47"/>
+      <c r="B1" s="48"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
@@ -38534,14 +38516,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47"/>
-      <c r="B11" s="47"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="47"/>
+      <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
@@ -38552,14 +38534,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="47"/>
+      <c r="B15" s="48"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
@@ -38586,14 +38568,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="47"/>
+      <c r="B20" s="48"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
@@ -38604,14 +38586,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="47"/>
+      <c r="B23" s="48"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
@@ -38638,14 +38620,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="47"/>
+      <c r="B28" s="48"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
@@ -38664,14 +38646,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="47"/>
+      <c r="B32" s="48"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">

--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\Desktop\Thư mục mới\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9836C0-8DD2-479F-9958-98DCD1F96662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5BF912-072B-4DCF-AAAB-423C5402231D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách trường Hàn" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="431">
   <si>
     <t>Daewon 대원대학교  |  Chi phí thấp - Hỗ trợ E7 liên kết Samsung &amp; Hyundai - Có thể học Online</t>
   </si>
@@ -2091,6 +2091,39 @@
 - Điều kiện chuyển: Hoàn thành khóa tiếng, đủ điều kiện từ trường
 - Học bổng chuyên ngành kỳ đầu tiên: Giảm 50%
 - Học bổng các kỳ tiếp theo: 30%–60% tùy trình độ TOPIK</t>
+  </si>
+  <si>
+    <t>Khu vực</t>
+  </si>
+  <si>
+    <t>Chungcheongbuk</t>
+  </si>
+  <si>
+    <t>Khu Vực</t>
+  </si>
+  <si>
+    <t>Gyeonggi</t>
+  </si>
+  <si>
+    <t>Seoul</t>
+  </si>
+  <si>
+    <t>Incheon</t>
+  </si>
+  <si>
+    <t>Busan</t>
+  </si>
+  <si>
+    <t>Jeollanam</t>
+  </si>
+  <si>
+    <t>Gyeongsangnam</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
   </si>
 </sst>
 </file>
@@ -3343,7 +3376,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3407,361 +3440,369 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="345" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3769,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3833,362 +3874,370 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4196,7 +4245,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -4260,362 +4309,370 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4623,7 +4680,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -4687,361 +4744,369 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5049,7 +5114,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5113,361 +5178,369 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5475,7 +5548,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5539,360 +5612,368 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="300" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="300" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18"/>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="B29" s="18"/>
+    </row>
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0E00-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0E00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5900,7 +5981,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5964,361 +6045,369 @@
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6326,7 +6415,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -6390,358 +6479,366 @@
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B10" s="37" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B13" s="37" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B16" s="37" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="220.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+    <row r="17" spans="1:2" ht="220.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B17" s="37" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+    <row r="18" spans="1:2" ht="109.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B18" s="37" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B21" s="37" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B24" s="37" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+    <row r="25" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B25" s="37" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+    <row r="26" spans="1:2" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B26" s="37" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B29" s="37" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B30" s="39" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B33" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C33" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B34" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C34" s="41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B35" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C35" s="43" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B36" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C36" s="41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B37" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C37" s="43" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B38" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C38" s="41" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B39" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C39" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="B40" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C40" s="41" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B41" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C41" s="43" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B42" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C42" s="41" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B43" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C43" s="43" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="40" t="s">
+      <c r="B44" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="41" t="s">
+      <c r="C44" s="41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B45" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C45" s="43" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="40" t="s">
+      <c r="B46" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C46" s="41" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B47" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C47" s="43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="40" t="s">
+      <c r="B48" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C48" s="41" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B49" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="43" t="s">
+      <c r="C49" s="43" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
@@ -6752,7 +6849,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -6818,357 +6915,365 @@
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18"/>
-    </row>
-    <row r="29" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="B29" s="18"/>
+    </row>
+    <row r="30" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="44" t="s">
+      <c r="B30" s="44" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B33" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C33" s="27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B34" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C34" s="41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B35" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C35" s="43" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B36" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C36" s="41" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B37" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="43" t="s">
+      <c r="C37" s="43" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B38" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C38" s="41" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B39" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="43" t="s">
+      <c r="C39" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="B40" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C40" s="41" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B41" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C41" s="43" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B42" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C42" s="41" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B43" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="43" t="s">
+      <c r="C43" s="43" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="40" t="s">
+      <c r="B44" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="41" t="s">
+      <c r="C44" s="41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B45" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="43" t="s">
+      <c r="C45" s="43" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="40" t="s">
+      <c r="B46" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C46" s="41" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B47" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="43" t="s">
+      <c r="C47" s="43" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="40" t="s">
+      <c r="B48" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C48" s="41" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B49" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="43" t="s">
+      <c r="C49" s="43" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
     <hyperlink ref="B8" r:id="rId2" xr:uid="{8524213D-53DA-45A7-838A-F509C2C59E98}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35447,7 +35552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -35513,359 +35618,367 @@
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35873,7 +35986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -35937,362 +36050,370 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="248.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="248.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="400.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B28" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36300,7 +36421,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -36364,362 +36485,370 @@
         <v>178</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B28" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36727,7 +36856,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -36791,362 +36920,370 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B29" s="18" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37154,7 +37291,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -37220,361 +37357,369 @@
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="358.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="B28" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="B29" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37582,7 +37727,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -37646,360 +37791,368 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="317.39999999999998" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="372.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+      <c r="B26" s="18"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B28" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="B29" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38007,7 +38160,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -38071,363 +38224,371 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B10" s="18" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-    </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B16" s="18" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+    </row>
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:3" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B21" s="18" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="48"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:3" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B24" s="18" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-    </row>
-    <row r="27" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
+    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+    </row>
+    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+    <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B30" s="34" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+    </row>
+    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C33" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B35" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C35" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B36" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B37" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C37" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C39" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C41" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="B42" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B43" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C43" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B44" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B45" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C45" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="B46" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B47" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C47" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B49" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C49" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-    <hyperlink ref="B28" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
-    <hyperlink ref="B29" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="B30" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38435,7 +38596,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -38507,363 +38668,371 @@
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B11" s="18" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+    <row r="12" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="48"/>
+      <c r="B12" s="48"/>
+    </row>
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
-    </row>
-    <row r="13" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="B13" s="48"/>
+    </row>
+    <row r="14" spans="1:2" ht="193.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B14" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50" t="s">
+    <row r="15" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
-    </row>
-    <row r="16" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="B16" s="48"/>
+    </row>
+    <row r="17" spans="1:2" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="18" spans="1:2" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+    <row r="19" spans="1:2" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B19" s="18" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-    </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+    <row r="20" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
+    </row>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
-    </row>
-    <row r="21" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="B21" s="48"/>
+    </row>
+    <row r="22" spans="1:2" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B22" s="18" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
+    <row r="23" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
+    </row>
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
-    </row>
-    <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="B24" s="48"/>
+    </row>
+    <row r="25" spans="1:2" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+    <row r="26" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B26" s="18" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B27" s="18" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-    </row>
-    <row r="28" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
+    <row r="28" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
+    </row>
+    <row r="29" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
-    </row>
-    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>256</v>
-      </c>
+      <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B31" s="18" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-    </row>
-    <row r="32" spans="1:2" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="47" t="s">
+    <row r="32" spans="1:2" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+    </row>
+    <row r="33" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
-    </row>
-    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="B33" s="48"/>
+    </row>
+    <row r="34" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B34" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C34" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B35" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C35" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B36" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C36" s="26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B37" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C37" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B38" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C38" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B39" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C39" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B40" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C40" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B41" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C41" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B42" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C42" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B43" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C43" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B44" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C44" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B45" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C45" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24" t="s">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B46" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C46" s="26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="B47" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C47" s="23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B48" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C48" s="26" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B49" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C49" s="23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B50" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C50" s="26" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
     <hyperlink ref="B9" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
-    <hyperlink ref="B29" r:id="rId3" xr:uid="{00000000-0004-0000-0800-000002000000}"/>
+    <hyperlink ref="B30" r:id="rId3" xr:uid="{00000000-0004-0000-0800-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
+++ b/Thong_tin_truong_Han_ky_thang_3_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phant\Desktop\Thư mục mới\thong-tin-truong-han\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB5E973-7475-4695-9939-5F2938E1CD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122B0202-9B72-4C44-BF17-3774D4D2A7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="884" firstSheet="11" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,20 @@
     <sheet name="ĐH Jeonju" sheetId="20" r:id="rId19"/>
     <sheet name="Check list HS xin Visa D2-6" sheetId="19" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2561,29 +2574,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2591,12 +2585,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2610,6 +2598,31 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2979,13 +2992,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.950000000000003" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1">
       <c r="A2" s="27" t="s">
@@ -3277,11 +3290,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="30" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
     </row>
     <row r="20" spans="1:5" ht="22.05" customHeight="1">
       <c r="A20" s="45" t="s">
@@ -3548,20 +3561,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -3620,14 +3633,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="409.2" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -3638,14 +3651,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -3672,14 +3685,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="345" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -3690,14 +3703,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="135" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -3724,14 +3737,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -3750,14 +3763,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -3983,20 +3996,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -4055,14 +4068,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="193.2" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -4073,14 +4086,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -4107,14 +4120,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -4125,14 +4138,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="105" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -4159,14 +4172,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -4185,14 +4198,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -4419,20 +4432,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -4491,14 +4504,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="150" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -4509,14 +4522,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -4543,14 +4556,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -4561,14 +4574,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="120" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -4595,14 +4608,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -4621,14 +4634,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -4855,20 +4868,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -4927,14 +4940,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="150" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -4945,14 +4958,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -4979,14 +4992,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -4997,14 +5010,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="105" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -5031,14 +5044,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -5057,14 +5070,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -5290,20 +5303,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -5362,14 +5375,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="150" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -5380,14 +5393,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -5414,14 +5427,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -5432,14 +5445,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="105" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -5466,14 +5479,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -5492,14 +5505,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -5725,20 +5738,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -5797,14 +5810,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="400.2" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -5815,14 +5828,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -5849,14 +5862,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="300" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -5867,14 +5880,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="135" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -5901,14 +5914,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -5925,14 +5938,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -6159,20 +6172,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -6231,14 +6244,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="193.2" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -6249,14 +6262,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -6283,14 +6296,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -6301,14 +6314,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="105" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -6335,14 +6348,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -6361,14 +6374,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -6594,20 +6607,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1">
       <c r="A4" s="36" t="s">
@@ -6666,14 +6679,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="303.60000000000002" customHeight="1">
       <c r="A13" s="36" t="s">
@@ -6684,14 +6697,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="180" customHeight="1">
       <c r="A16" s="36" t="s">
@@ -6718,14 +6731,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" customHeight="1">
       <c r="A21" s="36" t="s">
@@ -6736,14 +6749,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="180" customHeight="1">
       <c r="A24" s="36" t="s">
@@ -6770,14 +6783,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="36" t="s">
@@ -6796,14 +6809,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="27" t="s">
@@ -7029,20 +7042,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -7101,14 +7114,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="207" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -7119,14 +7132,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -7153,14 +7166,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="372.6" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -7171,14 +7184,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -7205,14 +7218,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -7229,14 +7242,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="27" t="s">
@@ -7457,450 +7470,456 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="36" style="54" customWidth="1"/>
-    <col min="2" max="2" width="70" style="54" customWidth="1"/>
-    <col min="3" max="3" width="50" style="54" customWidth="1"/>
-    <col min="4" max="16384" width="8.796875" style="54"/>
+    <col min="1" max="1" width="36" style="48" customWidth="1"/>
+    <col min="2" max="2" width="70" style="48" customWidth="1"/>
+    <col min="3" max="3" width="50" style="48" customWidth="1"/>
+    <col min="4" max="16384" width="8.796875" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.35" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="59" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="53"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="47"/>
     </row>
     <row r="2" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="53"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="47"/>
     </row>
     <row r="3" spans="1:3" ht="16.05" customHeight="1">
       <c r="A3" s="56" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="56"/>
-      <c r="C3" s="53"/>
+      <c r="C3" s="47"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="51" t="s">
         <v>432</v>
       </c>
-      <c r="C4" s="53"/>
+      <c r="C4" s="47"/>
     </row>
     <row r="5" spans="1:3" ht="24" customHeight="1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="53"/>
+      <c r="C5" s="47"/>
     </row>
     <row r="6" spans="1:3" ht="24" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="50" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="18">
         <v>200</v>
       </c>
-      <c r="C6" s="53"/>
+      <c r="C6" s="47"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="50" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="47"/>
     </row>
     <row r="8" spans="1:3" ht="24" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="50" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="44" t="s">
         <v>433</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="47"/>
     </row>
     <row r="9" spans="1:3" ht="24" customHeight="1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="51" t="s">
         <v>443</v>
       </c>
-      <c r="C9" s="53"/>
+      <c r="C9" s="47"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="51" t="s">
         <v>434</v>
       </c>
-      <c r="C10" s="53"/>
+      <c r="C10" s="47"/>
     </row>
     <row r="11" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="53"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="47"/>
     </row>
     <row r="12" spans="1:3" ht="16.05" customHeight="1">
       <c r="A12" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="56"/>
-      <c r="C12" s="53"/>
+      <c r="C12" s="47"/>
     </row>
     <row r="13" spans="1:3" ht="103.95" customHeight="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="51" t="s">
         <v>435</v>
       </c>
-      <c r="C13" s="53"/>
+      <c r="C13" s="47"/>
     </row>
     <row r="14" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A14" s="55"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="53"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="47"/>
     </row>
     <row r="15" spans="1:3" ht="16.05" customHeight="1">
       <c r="A15" s="56" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="56"/>
-      <c r="C15" s="53"/>
+      <c r="C15" s="47"/>
     </row>
     <row r="16" spans="1:3" ht="55.95" customHeight="1">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="51" t="s">
         <v>436</v>
       </c>
-      <c r="C16" s="53"/>
+      <c r="C16" s="47"/>
     </row>
     <row r="17" spans="1:3" ht="79.95" customHeight="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="51" t="s">
         <v>437</v>
       </c>
-      <c r="C17" s="53"/>
+      <c r="C17" s="47"/>
     </row>
     <row r="18" spans="1:3" ht="55.95" customHeight="1">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="51" t="s">
         <v>438</v>
       </c>
-      <c r="C18" s="53"/>
+      <c r="C18" s="47"/>
     </row>
     <row r="19" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="53"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="47"/>
     </row>
     <row r="20" spans="1:3" ht="16.05" customHeight="1">
       <c r="A20" s="56" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="53"/>
+      <c r="C20" s="47"/>
     </row>
     <row r="21" spans="1:3" ht="175.95" customHeight="1">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="C21" s="53"/>
+      <c r="C21" s="47"/>
     </row>
     <row r="22" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A22" s="55"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="53"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="47"/>
     </row>
     <row r="23" spans="1:3" ht="16.05" customHeight="1">
       <c r="A23" s="56" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="56"/>
-      <c r="C23" s="53"/>
+      <c r="C23" s="47"/>
     </row>
     <row r="24" spans="1:3" ht="96" customHeight="1">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="51" t="s">
         <v>440</v>
       </c>
-      <c r="C24" s="53"/>
+      <c r="C24" s="47"/>
     </row>
     <row r="25" spans="1:3" ht="103.95" customHeight="1">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="C25" s="53"/>
+      <c r="C25" s="47"/>
     </row>
     <row r="26" spans="1:3" ht="103.95" customHeight="1">
-      <c r="A26" s="57" t="s">
+      <c r="A26" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="51" t="s">
         <v>442</v>
       </c>
-      <c r="C26" s="53"/>
+      <c r="C26" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A27" s="55"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="53"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="16.05" customHeight="1">
       <c r="A28" s="56" t="s">
         <v>33</v>
       </c>
       <c r="B28" s="56"/>
-      <c r="C28" s="53"/>
+      <c r="C28" s="47"/>
     </row>
     <row r="29" spans="1:3" ht="16.05" customHeight="1">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="50" t="s">
         <v>34</v>
       </c>
       <c r="B29" s="44" t="s">
         <v>445</v>
       </c>
-      <c r="C29" s="53"/>
+      <c r="C29" s="47"/>
     </row>
     <row r="30" spans="1:3" ht="16.05" customHeight="1">
-      <c r="A30" s="57" t="s">
+      <c r="A30" s="50" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="C30" s="53"/>
+      <c r="C30" s="47"/>
     </row>
     <row r="31" spans="1:3" ht="4.8" customHeight="1">
-      <c r="A31" s="55"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="53"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="47"/>
     </row>
     <row r="32" spans="1:3" ht="16.05" customHeight="1">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="59"/>
-      <c r="C32" s="53"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="47"/>
     </row>
     <row r="33" spans="1:3" ht="16.05" customHeight="1">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="60" t="s">
+      <c r="C33" s="49" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A34" s="61" t="s">
+      <c r="A34" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="62" t="s">
+      <c r="B34" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="62" t="s">
+      <c r="C34" s="53" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="55" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="53" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="64" t="s">
+      <c r="B37" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="64" t="s">
+      <c r="C37" s="55" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A38" s="61" t="s">
+      <c r="A38" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="62" t="s">
+      <c r="C38" s="53" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="64" t="s">
+      <c r="B39" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="55" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="62" t="s">
+      <c r="C40" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A41" s="63" t="s">
+      <c r="A41" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="55" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A42" s="61" t="s">
+      <c r="A42" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="62" t="s">
+      <c r="C42" s="53" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A43" s="63" t="s">
+      <c r="A43" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="64" t="s">
+      <c r="B43" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="55" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A44" s="61" t="s">
+      <c r="A44" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="62" t="s">
+      <c r="C44" s="53" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A45" s="63" t="s">
+      <c r="A45" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="64" t="s">
+      <c r="B45" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="55" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A46" s="61" t="s">
+      <c r="A46" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="62" t="s">
+      <c r="B46" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="53" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A47" s="63" t="s">
+      <c r="A47" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="64" t="s">
+      <c r="C47" s="55" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A48" s="61" t="s">
+      <c r="A48" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B48" s="62" t="s">
+      <c r="B48" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="62" t="s">
+      <c r="C48" s="53" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14.4" customHeight="1">
-      <c r="A49" s="63" t="s">
+      <c r="A49" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="64" t="s">
+      <c r="C49" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="53"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
@@ -7910,12 +7929,6 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B30" r:id="rId1" xr:uid="{8E46879D-E49B-4394-B81D-ABE38B03AD1F}"/>
@@ -7938,20 +7951,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="27.6" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -8010,14 +8023,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="207" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -8028,14 +8041,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -8062,14 +8075,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="372.6" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -8080,14 +8093,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -8114,14 +8127,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -8140,14 +8153,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -36644,20 +36657,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -36716,14 +36729,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="248.4" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -36734,14 +36747,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="96.6" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -36768,14 +36781,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="400.2" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -36786,14 +36799,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="138" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -36820,14 +36833,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -36846,14 +36859,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -37080,20 +37093,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -37152,14 +37165,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="345" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -37170,14 +37183,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -37204,14 +37217,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -37222,14 +37235,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="135" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -37256,14 +37269,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -37282,14 +37295,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -37516,20 +37529,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -37588,14 +37601,14 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="207" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -37606,14 +37619,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="110.4" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -37640,14 +37653,14 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="303.60000000000002" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -37658,14 +37671,14 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="82.8" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -37692,14 +37705,14 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -37718,14 +37731,14 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -37952,20 +37965,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -38024,14 +38037,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="358.8" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -38042,14 +38055,14 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="138" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -38076,14 +38089,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="358.8" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -38094,14 +38107,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="90" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -38128,14 +38141,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -38154,14 +38167,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -38389,20 +38402,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -38461,14 +38474,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="317.39999999999998" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -38479,14 +38492,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="105" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -38513,14 +38526,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="372.6" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -38531,14 +38544,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="151.80000000000001" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -38563,14 +38576,14 @@
       <c r="B26" s="18"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -38589,14 +38602,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -38823,20 +38836,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -38895,14 +38908,14 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="6" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="207" customHeight="1">
       <c r="A13" s="17" t="s">
@@ -38913,14 +38926,14 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="6" customHeight="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="61"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="48"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="110.4" customHeight="1">
       <c r="A16" s="17" t="s">
@@ -38947,14 +38960,14 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="6" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="48"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="409.6" customHeight="1">
       <c r="A21" s="17" t="s">
@@ -38965,14 +38978,14 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="6" customHeight="1">
-      <c r="A22" s="48"/>
-      <c r="B22" s="48"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="110.4" customHeight="1">
       <c r="A24" s="17" t="s">
@@ -38999,14 +39012,14 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="6" customHeight="1">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="61"/>
+      <c r="B27" s="61"/>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="48"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1">
       <c r="A29" s="17" t="s">
@@ -39025,14 +39038,14 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="6" customHeight="1">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
+      <c r="A31" s="61"/>
+      <c r="B31" s="61"/>
     </row>
     <row r="32" spans="1:2" ht="25.05" customHeight="1">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="48"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="19.95" customHeight="1">
       <c r="A33" s="20" t="s">
@@ -39260,20 +39273,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="61"/>
     </row>
     <row r="2" spans="1:2" ht="6" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
+      <c r="B3" s="61"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -39340,14 +39353,14 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="6" customHeight="1">
-      <c r="A12" s="48"/>
-      <c r="B12" s="48"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="48"/>
+      <c r="B13" s="61"/>
     </row>
     <row r="14" spans="1:2" ht="193.2" customHeight="1">
       <c r="A14" s="17" t="s">
@@ -39358,14 +39371,14 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="6" customHeight="1">
-      <c r="A15" s="48"/>
-      <c r="B15" s="48"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="48"/>
+      <c r="B16" s="61"/>
     </row>
     <row r="17" spans="1:2" ht="96.6" customHeight="1">
       <c r="A17" s="17" t="s">
@@ -39392,14 +39405,14 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="6" customHeight="1">
-      <c r="A20" s="48"/>
-      <c r="B20" s="48"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="61"/>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="48"/>
+      <c r="B21" s="61"/>
     </row>
     <row r="22" spans="1:2" ht="409.6" customHeight="1">
       <c r="A22" s="17" t="s">
@@ -39410,14 +39423,14 @@
       </c>
     </row>
     <row r="23" spans="1:2" ht="6" customHeight="1">
-      <c r="A23" s="48"/>
-      <c r="B23" s="48"/>
+      <c r="A23" s="61"/>
+      <c r="B23" s="61"/>
     </row>
     <row r="24" spans="1:2" ht="30" customHeight="1">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="48"/>
+      <c r="B24" s="61"/>
     </row>
     <row r="25" spans="1:2" ht="151.80000000000001" customHeight="1">
       <c r="A25" s="17" t="s">
@@ -39444,14 +39457,14 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="6" customHeight="1">
-      <c r="A28" s="48"/>
-      <c r="B28" s="48"/>
+      <c r="A28" s="61"/>
+      <c r="B28" s="61"/>
     </row>
     <row r="29" spans="1:2" ht="30" customHeight="1">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="48"/>
+      <c r="B29" s="61"/>
     </row>
     <row r="30" spans="1:2" ht="18" customHeight="1">
       <c r="A30" s="17" t="s">
@@ -39470,14 +39483,14 @@
       </c>
     </row>
     <row r="32" spans="1:2" ht="6" customHeight="1">
-      <c r="A32" s="48"/>
-      <c r="B32" s="48"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="61"/>
     </row>
     <row r="33" spans="1:3" ht="25.05" customHeight="1">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="48"/>
+      <c r="B33" s="61"/>
     </row>
     <row r="34" spans="1:3" ht="19.95" customHeight="1">
       <c r="A34" s="20" t="s">
